--- a/output/pdf_financials_xlsx/RCI.B.xlsx
+++ b/output/pdf_financials_xlsx/RCI.B.xlsx
@@ -5742,13 +5742,13 @@
         <v>-3335</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-1885</v>
+        <v>-1886</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>-2387</v>
+        <v>-2466</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-2802</v>
+        <v>-2878</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>-1240</v>
@@ -5784,13 +5784,13 @@
         <v>-3335</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-1885</v>
+        <v>-1886</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-2387</v>
+        <v>-2466</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-2802</v>
+        <v>-2878</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>-1240</v>
@@ -54322,7 +54322,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">

--- a/output/pdf_financials_xlsx/RCI.B.xlsx
+++ b/output/pdf_financials_xlsx/RCI.B.xlsx
@@ -563,15 +563,11 @@
       <c r="J4" s="3" t="n">
         <v>19308</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="3" t="n">
+        <v>20604</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>21712</v>
       </c>
     </row>
     <row r="5">
@@ -609,15 +605,11 @@
       <c r="J5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -661,15 +653,11 @@
       <c r="J6" s="3" t="n">
         <v>19308</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="3" t="n">
+        <v>20604</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>21712</v>
       </c>
     </row>
     <row r="7">
@@ -707,15 +695,11 @@
       <c r="J7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -753,15 +737,11 @@
       <c r="J8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -799,15 +779,11 @@
       <c r="J9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -845,15 +821,11 @@
       <c r="J10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -891,15 +863,11 @@
       <c r="J11" s="3" t="n">
         <v>19308</v>
       </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K11" s="3" t="n">
+        <v>20604</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>21712</v>
       </c>
     </row>
     <row r="12">
@@ -937,15 +905,11 @@
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -983,15 +947,11 @@
       <c r="J13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1029,15 +989,11 @@
       <c r="J14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1075,15 +1031,11 @@
       <c r="J15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K15" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-5021</v>
       </c>
     </row>
     <row r="16">
@@ -1121,15 +1073,11 @@
       <c r="J16" s="3" t="n">
         <v>1366</v>
       </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>2306</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>7626</v>
       </c>
     </row>
     <row r="17">
@@ -1147,7 +1095,7 @@
         <v>-502</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-610</v>
+        <v>-43</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>545</v>
@@ -1167,15 +1115,11 @@
       <c r="J17" s="3" t="n">
         <v>-517</v>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="3" t="n">
+        <v>-572</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-720</v>
       </c>
     </row>
     <row r="18">
@@ -1337,15 +1281,11 @@
       <c r="J20" s="3" t="n">
         <v>849</v>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="3" t="n">
+        <v>1734</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>6906</v>
       </c>
     </row>
     <row r="21">
@@ -1383,15 +1323,11 @@
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1429,15 +1365,11 @@
       <c r="J22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="23">
@@ -1653,15 +1585,11 @@
       <c r="J27" s="3" t="n">
         <v>1366</v>
       </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K27" s="3" t="n">
+        <v>2306</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>7626</v>
       </c>
     </row>
     <row r="28">
@@ -1699,15 +1627,11 @@
       <c r="J28" s="3" t="n">
         <v>4121</v>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K28" s="3" t="n">
+        <v>4616</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>4802</v>
       </c>
     </row>
     <row r="29">
@@ -1745,15 +1669,11 @@
       <c r="J29" s="3" t="n">
         <v>5487</v>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K29" s="3" t="n">
+        <v>6922</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>12428</v>
       </c>
     </row>
     <row r="30">
@@ -1799,15 +1719,11 @@
       <c r="J30" s="3" t="n">
         <v>28.41827221876942</v>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K30" s="3" t="n">
+        <v>33.59541836536594</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>57.24023581429623</v>
       </c>
     </row>
     <row r="31">
@@ -1825,7 +1741,7 @@
         <v>25.35353535353536</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>28.53133769878391</v>
+        <v>2.011225444340505</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>25.52693208430913</v>
@@ -1845,15 +1761,11 @@
       <c r="J31" s="3" t="n">
         <v>37.84773060029283</v>
       </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v>24.80485689505637</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>9.441384736428009</v>
       </c>
     </row>
     <row r="32">
@@ -1899,15 +1811,11 @@
       <c r="J32" s="3" t="n">
         <v>4.397141081417029</v>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K32" s="3" t="n">
+        <v>8.415841584158416</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>31.80729550478998</v>
       </c>
     </row>
     <row r="33">
@@ -6279,7 +6187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O729"/>
+  <dimension ref="A1:O741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8128,7 +8036,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10659,7 +10571,11 @@
           <t>Lease liabilities 9 2,089</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -14671,7 +14587,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -43305,7 +43225,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E524" s="5" t="n">
         <v>421</v>
       </c>
@@ -44742,7 +44666,11 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr"/>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>beginning of the applicable trailing 12-month period.</t>
+        </is>
+      </c>
       <c r="C545" t="inlineStr">
         <is>
           <t>Revenue 6</t>
@@ -44788,21 +44716,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L545" s="5" t="n">
-        <v>15396</v>
-      </c>
-      <c r="M545" s="5" t="n">
-        <v>19308</v>
-      </c>
-      <c r="N545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N545" s="5" t="n">
+        <v>20604</v>
+      </c>
+      <c r="O545" s="5" t="n">
+        <v>21712</v>
       </c>
     </row>
     <row r="546">
@@ -44813,19 +44741,15 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 8, 9, 10</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Operating costs 7</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -44861,21 +44785,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L546" s="5" t="n">
-        <v>2576</v>
-      </c>
-      <c r="M546" s="5" t="n">
-        <v>4121</v>
-      </c>
-      <c r="N546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N546" s="5" t="n">
+        <v>10987</v>
+      </c>
+      <c r="O546" s="5" t="n">
+        <v>11892</v>
       </c>
     </row>
     <row r="547">
@@ -44886,15 +44810,19 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Restructuring, acquisition and other 11</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr"/>
+          <t>Depreciation and amortization 8, 9, 10</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -44930,21 +44858,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L547" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="M547" s="5" t="n">
-        <v>685</v>
-      </c>
-      <c r="N547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N547" s="5" t="n">
+        <v>4616</v>
+      </c>
+      <c r="O547" s="5" t="n">
+        <v>4802</v>
       </c>
     </row>
     <row r="548">
@@ -44955,12 +44883,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Finance costs 12</t>
+          <t>Restructuring, acquisition and other 11</t>
         </is>
       </c>
       <c r="D548" t="inlineStr"/>
@@ -44999,21 +44927,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L548" s="5" t="n">
-        <v>1233</v>
-      </c>
-      <c r="M548" s="5" t="n">
-        <v>2047</v>
-      </c>
-      <c r="N548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N548" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="O548" s="5" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="549">
@@ -45024,19 +44952,15 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Income before income tax expense</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Finance costs 12</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -45072,21 +44996,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L549" s="5" t="n">
-        <v>2289</v>
-      </c>
-      <c r="M549" s="5" t="n">
-        <v>1366</v>
-      </c>
-      <c r="N549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N549" s="5" t="n">
+        <v>2295</v>
+      </c>
+      <c r="O549" s="5" t="n">
+        <v>2043</v>
       </c>
     </row>
     <row r="550">
@@ -45097,19 +45021,15 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Income tax expense 14</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Gain on disposition of data centres 3</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -45145,21 +45065,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L550" s="5" t="n">
-        <v>609</v>
-      </c>
-      <c r="M550" s="5" t="n">
-        <v>517</v>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N550" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O550" s="5" t="n">
+        <v>-69</v>
       </c>
     </row>
     <row r="551">
@@ -45170,17 +45092,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
+          <t>Other income 13</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -45218,21 +45140,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L551" s="5" t="n">
-        <v>1680</v>
-      </c>
-      <c r="M551" s="5" t="n">
-        <v>849</v>
-      </c>
-      <c r="N551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N551" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O551" s="5" t="n">
+        <v>-5021</v>
       </c>
     </row>
     <row r="552">
@@ -45243,17 +45165,17 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Basic 15 $</t>
+          <t>Income before income tax expense</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -45286,26 +45208,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K552" s="5" t="n">
+        <v>2127</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>3.33e-06</v>
-      </c>
-      <c r="M552" s="5" t="n">
-        <v>1.62e-06</v>
-      </c>
-      <c r="N552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2289</v>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N552" s="5" t="n">
+        <v>2306</v>
+      </c>
+      <c r="O552" s="5" t="n">
+        <v>7626</v>
       </c>
     </row>
     <row r="553">
@@ -45316,17 +45234,17 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Diluted 15 $</t>
+          <t>Income tax expense 14</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -45364,21 +45282,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L553" s="5" t="n">
-        <v>3.32e-06</v>
-      </c>
-      <c r="M553" s="5" t="n">
-        <v>1.62e-06</v>
-      </c>
-      <c r="N553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N553" s="5" t="n">
+        <v>572</v>
+      </c>
+      <c r="O553" s="5" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="554">
@@ -45387,15 +45305,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr"/>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Revenue 5</t>
+          <t>Net income for the year</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -45429,25 +45351,21 @@
         </is>
       </c>
       <c r="K554" s="5" t="n">
-        <v>14655</v>
+        <v>1558</v>
       </c>
       <c r="L554" s="5" t="n">
-        <v>15396</v>
+        <v>1680</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N554" s="5" t="n">
+        <v>1734</v>
+      </c>
+      <c r="O554" s="5" t="n">
+        <v>6906</v>
       </c>
     </row>
     <row r="555">
@@ -45458,12 +45376,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net income for the year attributable to</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Operating costs 6</t>
+          <t>RCI shareholders</t>
         </is>
       </c>
       <c r="D555" t="inlineStr"/>
@@ -45497,26 +45415,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K555" s="5" t="n">
-        <v>8768</v>
-      </c>
-      <c r="L555" s="5" t="n">
-        <v>9003</v>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M555" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N555" s="5" t="n">
+        <v>1734</v>
+      </c>
+      <c r="O555" s="5" t="n">
+        <v>6894</v>
       </c>
     </row>
     <row r="556">
@@ -45527,17 +45445,17 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net income for the year attributable to</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 7, 8, 9</t>
+          <t>Non-controlling interest 30</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -45570,11 +45488,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K556" s="5" t="n">
-        <v>2585</v>
-      </c>
-      <c r="L556" s="5" t="n">
-        <v>2576</v>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M556" t="inlineStr">
         <is>
@@ -45586,10 +45508,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O556" s="5" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="557">
@@ -45600,12 +45520,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share attributable to RCI shareholders</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Restructuring, acquisition and other 10</t>
+          <t>Basic 15 $</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
@@ -45639,26 +45559,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K557" s="5" t="n">
-        <v>324</v>
-      </c>
-      <c r="L557" s="5" t="n">
-        <v>310</v>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M557" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N557" s="5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O557" s="5" t="n">
+        <v>12.77</v>
       </c>
     </row>
     <row r="558">
@@ -45669,12 +45589,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share attributable to RCI shareholders</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Finance costs 11</t>
+          <t>Diluted 15 $</t>
         </is>
       </c>
       <c r="D558" t="inlineStr"/>
@@ -45708,26 +45628,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K558" s="5" t="n">
-        <v>849</v>
-      </c>
-      <c r="L558" s="5" t="n">
-        <v>1233</v>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M558" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N558" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O558" s="5" t="n">
+        <v>12.74</v>
       </c>
     </row>
     <row r="559">
@@ -45736,19 +45656,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B559" t="inlineStr"/>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Other (income) expense 12</t>
+          <t>Revenue 6</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -45781,16 +45697,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K559" s="5" t="n">
-        <v>2</v>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L559" s="5" t="n">
-        <v>-15</v>
-      </c>
-      <c r="M559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15396</v>
+      </c>
+      <c r="M559" s="5" t="n">
+        <v>19308</v>
       </c>
       <c r="N559" t="inlineStr">
         <is>
@@ -45811,17 +45727,17 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Income before income tax expense</t>
+          <t>Depreciation and amortization 8, 9, 10</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -45854,16 +45770,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K560" s="5" t="n">
-        <v>2127</v>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L560" s="5" t="n">
-        <v>2289</v>
-      </c>
-      <c r="M560" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2576</v>
+      </c>
+      <c r="M560" s="5" t="n">
+        <v>4121</v>
       </c>
       <c r="N560" t="inlineStr">
         <is>
@@ -45884,19 +45800,15 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Income tax expense 13</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Restructuring, acquisition and other 11</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
@@ -45927,16 +45839,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K561" s="5" t="n">
-        <v>569</v>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L561" s="5" t="n">
-        <v>609</v>
-      </c>
-      <c r="M561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="M561" s="5" t="n">
+        <v>685</v>
       </c>
       <c r="N561" t="inlineStr">
         <is>
@@ -45957,19 +45869,15 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating expenses:    Operating costs                                                                         7       10,727         9,003                                       FINANCIAL</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Finance costs 12</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
           <t>-</t>
@@ -46000,16 +45908,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K562" s="5" t="n">
-        <v>1558</v>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L562" s="5" t="n">
-        <v>1680</v>
-      </c>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1233</v>
+      </c>
+      <c r="M562" s="5" t="n">
+        <v>2047</v>
       </c>
       <c r="N562" t="inlineStr">
         <is>
@@ -46030,17 +45938,17 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Basic 14 $</t>
+          <t>Income before income tax expense</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -46073,16 +45981,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K563" s="5" t="n">
-        <v>3.09e-06</v>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L563" s="5" t="n">
-        <v>3.33e-06</v>
-      </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2289</v>
+      </c>
+      <c r="M563" s="5" t="n">
+        <v>1366</v>
       </c>
       <c r="N563" t="inlineStr">
         <is>
@@ -46103,17 +46011,17 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Diluted 14 $</t>
+          <t>Income tax expense 14</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -46146,16 +46054,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K564" s="5" t="n">
-        <v>3.07e-06</v>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L564" s="5" t="n">
-        <v>3.32e-06</v>
-      </c>
-      <c r="M564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>609</v>
+      </c>
+      <c r="M564" s="5" t="n">
+        <v>517</v>
       </c>
       <c r="N564" t="inlineStr">
         <is>
@@ -46174,13 +46082,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr"/>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Other expense (income)                                                                      13         362             (15)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  STATEMENTS</t>
+        </is>
+      </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Operating costs 4</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr"/>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr">
         <is>
           <t>-</t>
@@ -46201,26 +46117,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I565" s="5" t="n">
-        <v>7729</v>
-      </c>
-      <c r="J565" s="5" t="n">
-        <v>7797</v>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L565" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="M565" s="5" t="n">
+        <v>849</v>
       </c>
       <c r="N565" t="inlineStr">
         <is>
@@ -46239,13 +46155,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr"/>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Restructuring, acquisition and other expenses 8</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr"/>
+          <t>Basic 15 $</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -46266,26 +46190,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I566" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="J566" s="5" t="n">
-        <v>85</v>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L566" s="5" t="n">
+        <v>3.33e-06</v>
+      </c>
+      <c r="M566" s="5" t="n">
+        <v>1.62e-06</v>
       </c>
       <c r="N566" t="inlineStr">
         <is>
@@ -46304,15 +46228,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr"/>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 12, 13</t>
+          <t>Diluted 15 $</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -46335,26 +46263,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I567" s="5" t="n">
-        <v>1819</v>
-      </c>
-      <c r="J567" s="5" t="n">
-        <v>1898</v>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L567" s="5" t="n">
+        <v>3.32e-06</v>
+      </c>
+      <c r="M567" s="5" t="n">
+        <v>1.62e-06</v>
       </c>
       <c r="N567" t="inlineStr">
         <is>
@@ -46373,19 +46301,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
-        </is>
-      </c>
+      <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Operating income</t>
+          <t>Revenue 5</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -46408,21 +46332,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I568" s="5" t="n">
-        <v>2766</v>
-      </c>
-      <c r="J568" s="5" t="n">
-        <v>2926</v>
-      </c>
-      <c r="K568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K568" s="5" t="n">
+        <v>14655</v>
+      </c>
+      <c r="L568" s="5" t="n">
+        <v>15396</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -46448,12 +46372,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Finance costs 5</t>
+          <t>Operating costs 6</t>
         </is>
       </c>
       <c r="D569" t="inlineStr"/>
@@ -46477,21 +46401,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I569" s="5" t="n">
-        <v>-671</v>
-      </c>
-      <c r="J569" s="5" t="n">
-        <v>-742</v>
-      </c>
-      <c r="K569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K569" s="5" t="n">
+        <v>8768</v>
+      </c>
+      <c r="L569" s="5" t="n">
+        <v>9003</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -46517,17 +46441,17 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Other income 7, 14, 25</t>
+          <t>Depreciation and amortization 7, 8, 9</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -46550,21 +46474,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I570" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J570" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="K570" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K570" s="5" t="n">
+        <v>2585</v>
+      </c>
+      <c r="L570" s="5" t="n">
+        <v>2576</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
@@ -46590,19 +46514,15 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Restructuring, acquisition and other 10</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -46623,21 +46543,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I571" s="5" t="n">
-        <v>2345</v>
-      </c>
-      <c r="J571" s="5" t="n">
-        <v>2265</v>
-      </c>
-      <c r="K571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K571" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="L571" s="5" t="n">
+        <v>310</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
@@ -46663,19 +46583,15 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Income tax expense 9</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Finance costs 11</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -46696,21 +46612,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I572" s="5" t="n">
-        <v>-620</v>
-      </c>
-      <c r="J572" s="5" t="n">
-        <v>-596</v>
-      </c>
-      <c r="K572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K572" s="5" t="n">
+        <v>849</v>
+      </c>
+      <c r="L572" s="5" t="n">
+        <v>1233</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
@@ -46736,17 +46652,17 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Net income from continuing operations</t>
+          <t>Other (income) expense 12</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -46769,21 +46685,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I573" s="5" t="n">
-        <v>1725</v>
-      </c>
-      <c r="J573" s="5" t="n">
-        <v>1669</v>
-      </c>
-      <c r="K573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K573" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L573" s="5" t="n">
+        <v>-15</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
@@ -46809,15 +46725,19 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Loss from discontinued operations, net of tax 6</t>
-        </is>
-      </c>
-      <c r="D574" t="inlineStr"/>
+          <t>Income tax expense 13</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
           <t>-</t>
@@ -46838,23 +46758,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I574" s="5" t="n">
-        <v>-32</v>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K574" s="5" t="n">
+        <v>569</v>
+      </c>
+      <c r="L574" s="5" t="n">
+        <v>609</v>
       </c>
       <c r="M574" t="inlineStr">
         <is>
@@ -46880,17 +46798,17 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Net income for the year $</t>
+          <t>Basic 14 $</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -46913,21 +46831,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I575" s="5" t="n">
-        <v>1693</v>
-      </c>
-      <c r="J575" s="5" t="n">
-        <v>1669</v>
-      </c>
-      <c r="K575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K575" s="5" t="n">
+        <v>3.09e-06</v>
+      </c>
+      <c r="L575" s="5" t="n">
+        <v>3.33e-06</v>
       </c>
       <c r="M575" t="inlineStr">
         <is>
@@ -46953,15 +46871,19 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Earnings per share – basic</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Earnings per share from continuing operations 10 $</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr"/>
+          <t>Diluted 14 $</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -46977,24 +46899,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H576" s="5" t="n">
-        <v>2.93e-06</v>
-      </c>
-      <c r="I576" s="5" t="n">
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K576" s="5" t="n">
+        <v>3.07e-06</v>
+      </c>
+      <c r="L576" s="5" t="n">
         <v>3.32e-06</v>
-      </c>
-      <c r="J576" s="5" t="n">
-        <v>3.24e-06</v>
-      </c>
-      <c r="K576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="M576" t="inlineStr">
         <is>
@@ -47018,14 +46942,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Earnings per share – basic</t>
-        </is>
-      </c>
+      <c r="B577" t="inlineStr"/>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Loss per share from discontinued operations 10</t>
+          <t>Operating costs 4</t>
         </is>
       </c>
       <c r="D577" t="inlineStr"/>
@@ -47044,16 +46964,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H577" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I577" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="J577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7729</v>
+      </c>
+      <c r="J577" s="5" t="n">
+        <v>7797</v>
       </c>
       <c r="K577" t="inlineStr">
         <is>
@@ -47087,21 +47007,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Earnings per share – basic</t>
-        </is>
-      </c>
+      <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Earnings per share – basic $</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Restructuring, acquisition and other expenses 8</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
@@ -47117,14 +47029,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H578" s="5" t="n">
-        <v>2.88e-06</v>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I578" s="5" t="n">
-        <v>3.26e-06</v>
+        <v>92</v>
       </c>
       <c r="J578" s="5" t="n">
-        <v>3.24e-06</v>
+        <v>85</v>
       </c>
       <c r="K578" t="inlineStr">
         <is>
@@ -47158,17 +47072,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Earnings per share – diluted</t>
-        </is>
-      </c>
+      <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Earnings per share from continuing operations 10 $</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr"/>
+          <t>Depreciation and amortization 12, 13</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -47184,14 +47098,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H579" s="5" t="n">
-        <v>2.91e-06</v>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I579" s="5" t="n">
-        <v>3.3e-06</v>
+        <v>1819</v>
       </c>
       <c r="J579" s="5" t="n">
-        <v>3.22e-06</v>
+        <v>1898</v>
       </c>
       <c r="K579" t="inlineStr">
         <is>
@@ -47227,15 +47143,19 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Earnings per share – diluted</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Loss per share from discontinued operations 10</t>
-        </is>
-      </c>
-      <c r="D580" t="inlineStr"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -47251,16 +47171,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H580" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I580" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="J580" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2766</v>
+      </c>
+      <c r="J580" s="5" t="n">
+        <v>2926</v>
       </c>
       <c r="K580" t="inlineStr">
         <is>
@@ -47296,19 +47216,15 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Earnings per share – diluted</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Earnings per share – diluted $</t>
-        </is>
-      </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Finance costs 5</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -47324,14 +47240,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H581" s="5" t="n">
-        <v>2.86e-06</v>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I581" s="5" t="n">
-        <v>3.24e-06</v>
+        <v>-671</v>
       </c>
       <c r="J581" s="5" t="n">
-        <v>3.22e-06</v>
+        <v>-742</v>
       </c>
       <c r="K581" t="inlineStr">
         <is>
@@ -47365,13 +47283,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr"/>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
+        </is>
+      </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Operating revenue 3(b) $</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr"/>
+          <t>Other income 7, 14, 25</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -47387,16 +47313,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H582" s="5" t="n">
-        <v>12346</v>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I582" s="5" t="n">
-        <v>12486</v>
-      </c>
-      <c r="J582" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>250</v>
+      </c>
+      <c r="J582" s="5" t="n">
+        <v>81</v>
       </c>
       <c r="K582" t="inlineStr">
         <is>
@@ -47432,15 +47358,19 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Operating costs 4</t>
-        </is>
-      </c>
-      <c r="D583" t="inlineStr"/>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>
@@ -47456,16 +47386,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H583" s="5" t="n">
-        <v>7682</v>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I583" s="5" t="n">
-        <v>7729</v>
-      </c>
-      <c r="J583" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2345</v>
+      </c>
+      <c r="J583" s="5" t="n">
+        <v>2265</v>
       </c>
       <c r="K583" t="inlineStr">
         <is>
@@ -47501,15 +47431,19 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Integration, restructuring and acquisition costs 8</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr"/>
+          <t>Income tax expense 9</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
           <t>-</t>
@@ -47525,16 +47459,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H584" s="5" t="n">
-        <v>56</v>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I584" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="J584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-620</v>
+      </c>
+      <c r="J584" s="5" t="n">
+        <v>-596</v>
       </c>
       <c r="K584" t="inlineStr">
         <is>
@@ -47570,17 +47504,17 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 12, 13</t>
+          <t>Net income from continuing operations</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>NetIncomeContinuousOperations</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -47598,16 +47532,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H585" s="5" t="n">
-        <v>1743</v>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I585" s="5" t="n">
-        <v>1819</v>
-      </c>
-      <c r="J585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1725</v>
+      </c>
+      <c r="J585" s="5" t="n">
+        <v>1669</v>
       </c>
       <c r="K585" t="inlineStr">
         <is>
@@ -47643,12 +47577,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Impairment of assets 13</t>
+          <t>Loss from discontinued operations, net of tax 6</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
@@ -47673,7 +47607,7 @@
         </is>
       </c>
       <c r="I586" s="5" t="n">
-        <v>80</v>
+        <v>-32</v>
       </c>
       <c r="J586" t="inlineStr">
         <is>
@@ -47714,17 +47648,17 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment of assets                                                                         13               –            80                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                STATEMENTS</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Operating income</t>
+          <t>Net income for the year $</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -47742,16 +47676,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H587" s="5" t="n">
-        <v>2865</v>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I587" s="5" t="n">
-        <v>2766</v>
-      </c>
-      <c r="J587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1693</v>
+      </c>
+      <c r="J587" s="5" t="n">
+        <v>1669</v>
       </c>
       <c r="K587" t="inlineStr">
         <is>
@@ -47787,12 +47721,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – basic</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Finance costs 5</t>
+          <t>Earnings per share from continuing operations 10 $</t>
         </is>
       </c>
       <c r="D588" t="inlineStr"/>
@@ -47812,15 +47746,13 @@
         </is>
       </c>
       <c r="H588" s="5" t="n">
-        <v>-738</v>
+        <v>2.93e-06</v>
       </c>
       <c r="I588" s="5" t="n">
-        <v>-664</v>
-      </c>
-      <c r="J588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.32e-06</v>
+      </c>
+      <c r="J588" s="5" t="n">
+        <v>3.24e-06</v>
       </c>
       <c r="K588" t="inlineStr">
         <is>
@@ -47856,12 +47788,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – basic</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Other income, net</t>
+          <t>Loss per share from discontinued operations 10</t>
         </is>
       </c>
       <c r="D589" t="inlineStr"/>
@@ -47881,10 +47813,10 @@
         </is>
       </c>
       <c r="H589" s="5" t="n">
-        <v>1</v>
+        <v>-5e-08</v>
       </c>
       <c r="I589" s="5" t="n">
-        <v>15</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="J589" t="inlineStr">
         <is>
@@ -47925,15 +47857,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – basic</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Share of the income of associates and joint ventures 24</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr"/>
+          <t>Earnings per share – basic $</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -47950,15 +47886,13 @@
         </is>
       </c>
       <c r="H590" s="5" t="n">
-        <v>7</v>
+        <v>2.88e-06</v>
       </c>
       <c r="I590" s="5" t="n">
-        <v>235</v>
-      </c>
-      <c r="J590" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.26e-06</v>
+      </c>
+      <c r="J590" s="5" t="n">
+        <v>3.24e-06</v>
       </c>
       <c r="K590" t="inlineStr">
         <is>
@@ -47994,19 +47928,15 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – diluted</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Earnings per share from continuing operations 10 $</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -48023,15 +47953,13 @@
         </is>
       </c>
       <c r="H591" s="5" t="n">
-        <v>2135</v>
+        <v>2.91e-06</v>
       </c>
       <c r="I591" s="5" t="n">
-        <v>2352</v>
-      </c>
-      <c r="J591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.3e-06</v>
+      </c>
+      <c r="J591" s="5" t="n">
+        <v>3.22e-06</v>
       </c>
       <c r="K591" t="inlineStr">
         <is>
@@ -48067,19 +47995,15 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – diluted</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Income tax expense 9</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Loss per share from discontinued operations 10</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -48096,10 +48020,10 @@
         </is>
       </c>
       <c r="H592" s="5" t="n">
-        <v>-545</v>
+        <v>-5e-08</v>
       </c>
       <c r="I592" s="5" t="n">
-        <v>-620</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="J592" t="inlineStr">
         <is>
@@ -48140,17 +48064,17 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Earnings per share – diluted</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Net income from continuing operations</t>
+          <t>Earnings per share – diluted $</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -48169,15 +48093,13 @@
         </is>
       </c>
       <c r="H593" s="5" t="n">
-        <v>1590</v>
+        <v>2.86e-06</v>
       </c>
       <c r="I593" s="5" t="n">
-        <v>1732</v>
-      </c>
-      <c r="J593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.24e-06</v>
+      </c>
+      <c r="J593" s="5" t="n">
+        <v>3.22e-06</v>
       </c>
       <c r="K593" t="inlineStr">
         <is>
@@ -48211,14 +48133,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Loss from discontinued operations, net of tax 6</t>
+          <t>Operating revenue 3(b) $</t>
         </is>
       </c>
       <c r="D594" t="inlineStr"/>
@@ -48238,10 +48156,10 @@
         </is>
       </c>
       <c r="H594" s="5" t="n">
-        <v>-27</v>
+        <v>12346</v>
       </c>
       <c r="I594" s="5" t="n">
-        <v>-32</v>
+        <v>12486</v>
       </c>
       <c r="J594" t="inlineStr">
         <is>
@@ -48287,14 +48205,10 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Net income for the year $</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Operating costs 4</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -48311,10 +48225,10 @@
         </is>
       </c>
       <c r="H595" s="5" t="n">
-        <v>1563</v>
+        <v>7682</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>1700</v>
+        <v>7729</v>
       </c>
       <c r="J595" t="inlineStr">
         <is>
@@ -48360,7 +48274,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Operating costs (note 5) 7,787</t>
+          <t>Integration, restructuring and acquisition costs 8</t>
         </is>
       </c>
       <c r="D596" t="inlineStr"/>
@@ -48380,12 +48294,10 @@
         </is>
       </c>
       <c r="H596" s="5" t="n">
-        <v>7571</v>
-      </c>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="I596" s="5" t="n">
+        <v>92</v>
       </c>
       <c r="J596" t="inlineStr">
         <is>
@@ -48431,10 +48343,14 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Impairment of assets (note 13) –</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr"/>
+          <t>Depreciation and amortization 12, 13</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -48451,12 +48367,10 @@
         </is>
       </c>
       <c r="H597" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1743</v>
+      </c>
+      <c r="I597" s="5" t="n">
+        <v>1819</v>
       </c>
       <c r="J597" t="inlineStr">
         <is>
@@ -48502,14 +48416,10 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Other income (expense), net 1</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Impairment of assets 13</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
           <t>-</t>
@@ -48525,13 +48435,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H598" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I598" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I598" s="5" t="n">
+        <v>80</v>
       </c>
       <c r="J598" t="inlineStr">
         <is>
@@ -48577,10 +48487,14 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Share of the income of associates and joint ventures accounted for using the equity method, net of tax 7</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
@@ -48597,12 +48511,10 @@
         </is>
       </c>
       <c r="H599" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I599" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2865</v>
+      </c>
+      <c r="I599" s="5" t="n">
+        <v>2766</v>
       </c>
       <c r="J599" t="inlineStr">
         <is>
@@ -48648,14 +48560,10 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Income before income taxes 2,098</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Finance costs 5</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -48672,12 +48580,10 @@
         </is>
       </c>
       <c r="H600" s="5" t="n">
-        <v>2114</v>
-      </c>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-738</v>
+      </c>
+      <c r="I600" s="5" t="n">
+        <v>-664</v>
       </c>
       <c r="J600" t="inlineStr">
         <is>
@@ -48723,14 +48629,10 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Income tax expense (note 9) 535</t>
-        </is>
-      </c>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Other income, net</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
           <t>-</t>
@@ -48747,12 +48649,10 @@
         </is>
       </c>
       <c r="H601" s="5" t="n">
-        <v>612</v>
-      </c>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I601" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="J601" t="inlineStr">
         <is>
@@ -48798,14 +48698,10 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Net income for the year $ 1,563 $</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share of the income of associates and joint ventures 24</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
@@ -48822,12 +48718,10 @@
         </is>
       </c>
       <c r="H602" s="5" t="n">
-        <v>1502</v>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="I602" s="5" t="n">
+        <v>235</v>
       </c>
       <c r="J602" t="inlineStr">
         <is>
@@ -48868,15 +48762,19 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Basic $ 2.88 $</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr"/>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -48893,12 +48791,10 @@
         </is>
       </c>
       <c r="H603" s="5" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2135</v>
+      </c>
+      <c r="I603" s="5" t="n">
+        <v>2352</v>
       </c>
       <c r="J603" t="inlineStr">
         <is>
@@ -48939,15 +48835,19 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Diluted 2.86</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr"/>
+          <t>Income tax expense 9</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
           <t>-</t>
@@ -48964,12 +48864,10 @@
         </is>
       </c>
       <c r="H604" s="5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-545</v>
+      </c>
+      <c r="I604" s="5" t="n">
+        <v>-620</v>
       </c>
       <c r="J604" t="inlineStr">
         <is>
@@ -49008,15 +48906,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B605" t="inlineStr"/>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Operating revenue (note 3(b)) $</t>
+          <t>Net income from continuing operations</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>OperatingRevenue</t>
+          <t>NetIncomeContinuousOperations</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -49024,21 +48926,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F605" s="5" t="n">
-        <v>11731</v>
-      </c>
-      <c r="G605" s="5" t="n">
-        <v>12186</v>
-      </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H605" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="I605" s="5" t="n">
+        <v>1732</v>
       </c>
       <c r="J605" t="inlineStr">
         <is>
@@ -49084,34 +48986,30 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Loss from discontinued operations, net of tax 6</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F606" s="5" t="n">
-        <v>1380</v>
-      </c>
-      <c r="G606" s="5" t="n">
-        <v>1520</v>
-      </c>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I606" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H606" s="5" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I606" s="5" t="n">
+        <v>-32</v>
       </c>
       <c r="J606" t="inlineStr">
         <is>
@@ -49157,12 +49055,12 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
+          <t>Net income for the year $</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>SellingAndMarketingExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -49170,21 +49068,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F607" s="5" t="n">
-        <v>1207</v>
-      </c>
-      <c r="G607" s="5" t="n">
-        <v>1227</v>
-      </c>
-      <c r="H607" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I607" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H607" s="5" t="n">
+        <v>1563</v>
+      </c>
+      <c r="I607" s="5" t="n">
+        <v>1700</v>
       </c>
       <c r="J607" t="inlineStr">
         <is>
@@ -49230,29 +49128,27 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Operating, general and administrative</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Operating costs (note 5) 7,787</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F608" s="5" t="n">
-        <v>4681</v>
-      </c>
-      <c r="G608" s="5" t="n">
-        <v>4847</v>
-      </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H608" s="5" t="n">
+        <v>7571</v>
       </c>
       <c r="I608" t="inlineStr">
         <is>
@@ -49303,7 +49199,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Settlement of pension obligations (note 17(d))</t>
+          <t>Impairment of assets (note 13) –</t>
         </is>
       </c>
       <c r="D609" t="inlineStr"/>
@@ -49312,18 +49208,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F609" s="5" t="n">
-        <v>30</v>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H609" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="I609" t="inlineStr">
         <is>
@@ -49374,25 +49270,31 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Integration and restructuring (note 6)</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr"/>
+          <t>Other income (expense), net 1</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E610" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F610" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="G610" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H610" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="I610" t="inlineStr">
         <is>
@@ -49443,29 +49345,27 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Share of the income of associates and joint ventures accounted for using the equity method, net of tax 7</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F611" s="5" t="n">
-        <v>1730</v>
-      </c>
-      <c r="G611" s="5" t="n">
-        <v>1645</v>
-      </c>
-      <c r="H611" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H611" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -49511,30 +49411,36 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets and other long-term assets (notes 11(a) and 13)</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr"/>
+          <t>Income before income taxes 2,098</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F612" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G612" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H612" s="5" t="n">
+        <v>2114</v>
       </c>
       <c r="I612" t="inlineStr">
         <is>
@@ -49580,17 +49486,17 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Operating income</t>
+          <t>Income tax expense (note 9) 535</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -49598,16 +49504,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F613" s="5" t="n">
-        <v>2568</v>
-      </c>
-      <c r="G613" s="5" t="n">
-        <v>2901</v>
-      </c>
-      <c r="H613" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H613" s="5" t="n">
+        <v>612</v>
       </c>
       <c r="I613" t="inlineStr">
         <is>
@@ -49653,30 +49561,36 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Interest on long-term debt</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr"/>
+          <t>Net income for the year $ 1,563 $</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F614" s="5" t="n">
-        <v>-647</v>
-      </c>
-      <c r="G614" s="5" t="n">
-        <v>-669</v>
-      </c>
-      <c r="H614" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="n">
+        <v>1502</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>
@@ -49722,12 +49636,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Debt issuance costs (note 14(c))</t>
+          <t>Basic $ 2.88 $</t>
         </is>
       </c>
       <c r="D615" t="inlineStr"/>
@@ -49736,16 +49650,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F615" s="5" t="n">
-        <v>-11</v>
-      </c>
-      <c r="G615" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="n">
+        <v>2.61</v>
       </c>
       <c r="I615" t="inlineStr">
         <is>
@@ -49791,12 +49707,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Loss on repayment of long-term debt (note 14(d))</t>
+          <t>Diluted 2.86</t>
         </is>
       </c>
       <c r="D616" t="inlineStr"/>
@@ -49805,16 +49721,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F616" s="5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G616" s="5" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="n">
+        <v>2.59</v>
       </c>
       <c r="I616" t="inlineStr">
         <is>
@@ -49858,19 +49776,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
-        </is>
-      </c>
+      <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Operating revenue (note 3(b)) $</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingRevenue</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -49879,10 +49793,10 @@
         </is>
       </c>
       <c r="F617" s="5" t="n">
-        <v>136</v>
+        <v>11731</v>
       </c>
       <c r="G617" s="5" t="n">
-        <v>20</v>
+        <v>12186</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
@@ -49933,25 +49847,29 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Change in fair value of derivative instruments</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr"/>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E618" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F618" s="5" t="n">
-        <v>-65</v>
+        <v>1380</v>
       </c>
       <c r="G618" s="5" t="n">
-        <v>-16</v>
+        <v>1520</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
@@ -50002,17 +49920,17 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Sales and marketing</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingAndMarketingExpense</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -50021,10 +49939,10 @@
         </is>
       </c>
       <c r="F619" s="5" t="n">
-        <v>6</v>
+        <v>1207</v>
       </c>
       <c r="G619" s="5" t="n">
-        <v>-1</v>
+        <v>1227</v>
       </c>
       <c r="H619" t="inlineStr">
         <is>
@@ -50075,17 +49993,17 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
+          <t>Operating, general and administrative</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -50094,10 +50012,10 @@
         </is>
       </c>
       <c r="F620" s="5" t="n">
-        <v>1980</v>
+        <v>4681</v>
       </c>
       <c r="G620" s="5" t="n">
-        <v>2138</v>
+        <v>4847</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
@@ -50148,12 +50066,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Settlement of pension obligations (note 17(d))</t>
         </is>
       </c>
       <c r="D621" t="inlineStr"/>
@@ -50163,10 +50081,12 @@
         </is>
       </c>
       <c r="F621" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="G621" s="5" t="n">
-        <v>322</v>
+        <v>30</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -50217,12 +50137,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Integration and restructuring (note 6)</t>
         </is>
       </c>
       <c r="D622" t="inlineStr"/>
@@ -50232,10 +50152,10 @@
         </is>
       </c>
       <c r="F622" s="5" t="n">
-        <v>287</v>
+        <v>117</v>
       </c>
       <c r="G622" s="5" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
@@ -50286,17 +50206,17 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Net income for the year $</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -50305,10 +50225,10 @@
         </is>
       </c>
       <c r="F623" s="5" t="n">
-        <v>1478</v>
+        <v>1730</v>
       </c>
       <c r="G623" s="5" t="n">
-        <v>1528</v>
+        <v>1645</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
@@ -50359,29 +50279,25 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Impairment losses on goodwill, intangible assets and other long-term assets (notes 11(a) and 13)</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F624" s="5" t="n">
-        <v>2.38e-06</v>
+        <v>18</v>
       </c>
       <c r="G624" s="5" t="n">
-        <v>2.65e-06</v>
+        <v>6</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
@@ -50432,27 +50348,29 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RESULTS OF OPERATIONS</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED DECEMBER 31,</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F625" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F625" s="5" t="n">
+        <v>2568</v>
       </c>
       <c r="G625" s="5" t="n">
-        <v>2009</v>
+        <v>2901</v>
       </c>
       <c r="H625" t="inlineStr">
         <is>
@@ -50503,12 +50421,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>industry growth rates, currency exchange rates, product pricing</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>could cause actual results to differ materially from those in the</t>
+          <t>Interest on long-term debt</t>
         </is>
       </c>
       <c r="D626" t="inlineStr"/>
@@ -50517,13 +50435,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F626" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F626" s="5" t="n">
+        <v>-647</v>
       </c>
       <c r="G626" s="5" t="n">
-        <v>3042</v>
+        <v>-669</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
@@ -50574,12 +50490,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>forward-looking statements or could cause our current objectives</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>forward-looking statements or could cause our current objectives</t>
+          <t>Debt issuance costs (note 14(c))</t>
         </is>
       </c>
       <c r="D627" t="inlineStr"/>
@@ -50588,13 +50504,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F627" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F627" s="5" t="n">
+        <v>-11</v>
       </c>
       <c r="G627" s="5" t="n">
-        <v>1324</v>
+        <v>-10</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
@@ -50645,12 +50559,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>forward-looking statements or could cause our current objectives</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>and strategies to change, including but not limited to economic 1,317 1,496 1,407 176 142</t>
+          <t>Loss on repayment of long-term debt (note 14(d))</t>
         </is>
       </c>
       <c r="D628" t="inlineStr"/>
@@ -50659,13 +50573,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F628" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F628" s="5" t="n">
+        <v>-7</v>
       </c>
       <c r="G628" s="5" t="n">
-        <v>119</v>
+        <v>-87</v>
       </c>
       <c r="H628" t="inlineStr">
         <is>
@@ -50716,27 +50628,29 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>any other factors underlying the forward-looking statements</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>from what we currently foresee. Accordingly, we warn investors</t>
-        </is>
-      </c>
-      <c r="D629" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E629" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F629" s="5" t="n">
+        <v>136</v>
       </c>
       <c r="G629" s="5" t="n">
-        <v>20092009</v>
+        <v>20</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
@@ -50787,12 +50701,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>In millions of dollars (unaudited) Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec.</t>
+          <t>Change in fair value of derivative instruments</t>
         </is>
       </c>
       <c r="D630" t="inlineStr"/>
@@ -50801,13 +50715,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F630" s="5" t="n">
+        <v>-65</v>
       </c>
       <c r="G630" s="5" t="n">
-        <v>31</v>
+        <v>-16</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -50858,27 +50770,29 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Years ended December 31 (unaudited) 2009 2008 2007 2009 2008 2007 2009 2008</t>
-        </is>
-      </c>
-      <c r="D631" t="inlineStr"/>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F631" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="G631" s="5" t="n">
-        <v>2007</v>
+        <v>-1</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
@@ -50929,17 +50843,17 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Revenue $ 90 $ 83 $ 75 $ 8,884 $ 8,469 $ 7,461 $ 3,159 $ 3,186 $</t>
+          <t>Income before income taxes</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -50947,13 +50861,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F632" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="G632" s="5" t="n">
-        <v>2934</v>
+        <v>2138</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
@@ -51004,12 +50916,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Operating Income (loss) (133) (131) (352) 2,270 2,145 1,612 580 260</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D633" t="inlineStr"/>
@@ -51018,13 +50930,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F633" s="5" t="n">
+        <v>215</v>
       </c>
       <c r="G633" s="5" t="n">
-        <v>456</v>
+        <v>322</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
@@ -51075,12 +50985,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Net income (loss) 1,478 1,002 637 2,153 1,814 1,479 (498) (293)</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="D634" t="inlineStr"/>
@@ -51089,13 +50999,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F634" s="5" t="n">
+        <v>287</v>
       </c>
       <c r="G634" s="5" t="n">
-        <v>16</v>
+        <v>288</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
@@ -51146,27 +51054,29 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Current assets $ 3,339 $ 3,011 $ 3,622 $ 5,296 $ 3,253 $ 3,669 $ 3,349 $ 2,097 $</t>
-        </is>
-      </c>
-      <c r="D635" t="inlineStr"/>
+          <t>Net income for the year $</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F635" s="5" t="n">
+        <v>1478</v>
       </c>
       <c r="G635" s="5" t="n">
-        <v>2356</v>
+        <v>1528</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
@@ -51217,27 +51127,29 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>Net income per share</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Non-current assets 21,681 17,406 14,337 8,366 7,105 6,830 8,328 7,689</t>
-        </is>
-      </c>
-      <c r="D636" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F636" s="5" t="n">
+        <v>2.38e-06</v>
       </c>
       <c r="G636" s="5" t="n">
-        <v>5159</v>
+        <v>2.65e-06</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
@@ -51288,12 +51200,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RESULTS OF OPERATIONS</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Current liabilities 7,724 4,190 3,321 4,005 3,903 5,885 748 691</t>
+          <t>FOR THE YEAR ENDED DECEMBER 31,</t>
         </is>
       </c>
       <c r="D637" t="inlineStr"/>
@@ -51308,7 +51220,7 @@
         </is>
       </c>
       <c r="G637" s="5" t="n">
-        <v>1047</v>
+        <v>2009</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
@@ -51359,12 +51271,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>industry growth rates, currency exchange rates, product pricing</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Non-current liabilities 9,489 9,134 7,651 147 149 170 81 132</t>
+          <t>could cause actual results to differ materially from those in the</t>
         </is>
       </c>
       <c r="D638" t="inlineStr"/>
@@ -51379,7 +51291,7 @@
         </is>
       </c>
       <c r="G638" s="5" t="n">
-        <v>17</v>
+        <v>3042</v>
       </c>
       <c r="H638" t="inlineStr">
         <is>
@@ -51430,12 +51342,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>forward-looking statements or could cause our current objectives</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>In millions of dollars (unaudited) Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec.</t>
+          <t>forward-looking statements or could cause our current objectives</t>
         </is>
       </c>
       <c r="D639" t="inlineStr"/>
@@ -51450,7 +51362,7 @@
         </is>
       </c>
       <c r="G639" s="5" t="n">
-        <v>31</v>
+        <v>1324</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -51501,12 +51413,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>forward-looking statements or could cause our current objectives</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Years ended December 31 (unaudited) 2009 2008 2007 2009 2008</t>
+          <t>and strategies to change, including but not limited to economic 1,317 1,496 1,407 176 142</t>
         </is>
       </c>
       <c r="D640" t="inlineStr"/>
@@ -51521,7 +51433,7 @@
         </is>
       </c>
       <c r="G640" s="5" t="n">
-        <v>2007</v>
+        <v>119</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
@@ -51572,12 +51484,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>any other factors underlying the forward-looking statements</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Revenue $ (402) $ (403) $ (347) $ 11,731 $ 11,335 $</t>
+          <t>from what we currently foresee. Accordingly, we warn investors</t>
         </is>
       </c>
       <c r="D641" t="inlineStr"/>
@@ -51592,7 +51504,7 @@
         </is>
       </c>
       <c r="G641" s="5" t="n">
-        <v>10123</v>
+        <v>20092009</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
@@ -51643,12 +51555,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Operating Income (loss) (149) (250) (220) 2,568 2,024</t>
+          <t>In millions of dollars (unaudited) Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec.</t>
         </is>
       </c>
       <c r="D642" t="inlineStr"/>
@@ -51663,7 +51575,7 @@
         </is>
       </c>
       <c r="G642" s="5" t="n">
-        <v>1496</v>
+        <v>31</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
@@ -51714,12 +51626,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Net income (loss) (1,655) (1,521) (1,495) 1,478 1,002</t>
+          <t>Years ended December 31 (unaudited) 2009 2008 2007 2009 2008 2007 2009 2008</t>
         </is>
       </c>
       <c r="D643" t="inlineStr"/>
@@ -51734,7 +51646,7 @@
         </is>
       </c>
       <c r="G643" s="5" t="n">
-        <v>637</v>
+        <v>2007</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
@@ -51785,15 +51697,19 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Current assets $ (9,729) $ (6,065) $ (7,499) $ 2,255 $ 2,296 $</t>
-        </is>
-      </c>
-      <c r="D644" t="inlineStr"/>
+          <t>Revenue $ 90 $ 83 $ 75 $ 8,884 $ 8,469 $ 7,461 $ 3,159 $ 3,186 $</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
@@ -51805,7 +51721,7 @@
         </is>
       </c>
       <c r="G644" s="5" t="n">
-        <v>2148</v>
+        <v>2934</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
@@ -51856,12 +51772,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Non-current assets (23,612) (17,414) (13,160) 14,763 14,786</t>
+          <t>Operating Income (loss) (133) (131) (352) 2,270 2,145 1,612 580 260</t>
         </is>
       </c>
       <c r="D645" t="inlineStr"/>
@@ -51876,7 +51792,7 @@
         </is>
       </c>
       <c r="G645" s="5" t="n">
-        <v>13166</v>
+        <v>456</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
@@ -51927,12 +51843,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>(at period end)</t>
+          <t>RCI(1)(2)(3)(4)                                            Guarantors(1)(2)(3)(4)                       Other Subsidiaries (2)(3)(4)</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Current liabilities (9,729) (6,068) (7,511) 2,748 2,716</t>
+          <t>Net income (loss) 1,478 1,002 637 2,153 1,814 1,479 (498) (293)</t>
         </is>
       </c>
       <c r="D646" t="inlineStr"/>
@@ -51947,7 +51863,7 @@
         </is>
       </c>
       <c r="G646" s="5" t="n">
-        <v>2742</v>
+        <v>16</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
@@ -52003,7 +51919,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Non-current liabilities 280 235 121 9,997 9,650</t>
+          <t>Current assets $ 3,339 $ 3,011 $ 3,622 $ 5,296 $ 3,253 $ 3,669 $ 3,349 $ 2,097 $</t>
         </is>
       </c>
       <c r="D647" t="inlineStr"/>
@@ -52018,7 +51934,7 @@
         </is>
       </c>
       <c r="G647" s="5" t="n">
-        <v>7959</v>
+        <v>2356</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
@@ -52069,12 +51985,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>under any of RCI’s long-term debt.</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>$5 million increase in current assets, a $16 million decrease in non-current assets, and an $11 million decrease in retained earnings for the periods presented above prior to January 1,</t>
+          <t>Non-current assets 21,681 17,406 14,337 8,366 7,105 6,830 8,328 7,689</t>
         </is>
       </c>
       <c r="D648" t="inlineStr"/>
@@ -52089,7 +52005,7 @@
         </is>
       </c>
       <c r="G648" s="5" t="n">
-        <v>2009</v>
+        <v>5159</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -52140,12 +52056,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Operating Profit Margin Calculations</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Years ended December</t>
+          <t>Current liabilities 7,724 4,190 3,321 4,005 3,903 5,885 748 691</t>
         </is>
       </c>
       <c r="D649" t="inlineStr"/>
@@ -52160,7 +52076,7 @@
         </is>
       </c>
       <c r="G649" s="5" t="n">
-        <v>31</v>
+        <v>1047</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
@@ -52211,12 +52127,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Operating Profit Margin Calculations</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>(In millions of dollars) 2009</t>
+          <t>Non-current liabilities 9,489 9,134 7,651 147 149 170 81 132</t>
         </is>
       </c>
       <c r="D650" t="inlineStr"/>
@@ -52231,7 +52147,7 @@
         </is>
       </c>
       <c r="G650" s="5" t="n">
-        <v>2008</v>
+        <v>17</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
@@ -52282,19 +52198,15 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 4,388 $</t>
-        </is>
-      </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>In millions of dollars (unaudited) Dec.31 Dec. 31 Dec. 31 Dec.31 Dec. 31 Dec.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr">
         <is>
           <t>-</t>
@@ -52306,7 +52218,7 @@
         </is>
       </c>
       <c r="G651" s="5" t="n">
-        <v>4060</v>
+        <v>31</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
@@ -52357,19 +52269,15 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Divided by total revenue 11,731</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Years ended December 31 (unaudited) 2009 2008 2007 2009 2008</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
@@ -52381,7 +52289,7 @@
         </is>
       </c>
       <c r="G652" s="5" t="n">
-        <v>11335</v>
+        <v>2007</v>
       </c>
       <c r="H652" t="inlineStr">
         <is>
@@ -52432,19 +52340,15 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>WIRELESS</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 3,042 $</t>
-        </is>
-      </c>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Revenue $ (402) $ (403) $ (347) $ 11,731 $ 11,335 $</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
           <t>-</t>
@@ -52456,7 +52360,7 @@
         </is>
       </c>
       <c r="G653" s="5" t="n">
-        <v>2806</v>
+        <v>10123</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
@@ -52507,12 +52411,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>WIRELESS</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Divided by network revenue 6,245</t>
+          <t>Operating Income (loss) (149) (250) (220) 2,568 2,024</t>
         </is>
       </c>
       <c r="D654" t="inlineStr"/>
@@ -52527,7 +52431,7 @@
         </is>
       </c>
       <c r="G654" s="5" t="n">
-        <v>5843</v>
+        <v>1496</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
@@ -52578,19 +52482,15 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Cable Operations</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 1,298 $</t>
-        </is>
-      </c>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Net income (loss) (1,655) (1,521) (1,495) 1,478 1,002</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
           <t>-</t>
@@ -52602,7 +52502,7 @@
         </is>
       </c>
       <c r="G655" s="5" t="n">
-        <v>1171</v>
+        <v>637</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
@@ -52653,12 +52553,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Cable Operations</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Divided by revenue 3,074</t>
+          <t>Current assets $ (9,729) $ (6,065) $ (7,499) $ 2,255 $ 2,296 $</t>
         </is>
       </c>
       <c r="D656" t="inlineStr"/>
@@ -52673,7 +52573,7 @@
         </is>
       </c>
       <c r="G656" s="5" t="n">
-        <v>2878</v>
+        <v>2148</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
@@ -52724,19 +52624,15 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Rogers Business Solutions</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 35 $</t>
-        </is>
-      </c>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Non-current assets (23,612) (17,414) (13,160) 14,763 14,786</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
           <t>-</t>
@@ -52748,7 +52644,7 @@
         </is>
       </c>
       <c r="G657" s="5" t="n">
-        <v>59</v>
+        <v>13166</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
@@ -52799,12 +52695,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Rogers Business Solutions</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Divided by revenue 503</t>
+          <t>Current liabilities (9,729) (6,068) (7,511) 2,748 2,716</t>
         </is>
       </c>
       <c r="D658" t="inlineStr"/>
@@ -52819,7 +52715,7 @@
         </is>
       </c>
       <c r="G658" s="5" t="n">
-        <v>526</v>
+        <v>2742</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
@@ -52870,12 +52766,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Rogers Retail</t>
+          <t>(at period end)</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Adjusted operating profit (loss) $ (9) $</t>
+          <t>Non-current liabilities 280 235 121 9,997 9,650</t>
         </is>
       </c>
       <c r="D659" t="inlineStr"/>
@@ -52890,7 +52786,7 @@
         </is>
       </c>
       <c r="G659" s="5" t="n">
-        <v>3</v>
+        <v>7959</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
@@ -52941,12 +52837,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Rogers Retail</t>
+          <t>under any of RCI’s long-term debt.</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Divided by revenue 399</t>
+          <t>$5 million increase in current assets, a $16 million decrease in non-current assets, and an $11 million decrease in retained earnings for the periods presented above prior to January 1,</t>
         </is>
       </c>
       <c r="D660" t="inlineStr"/>
@@ -52961,7 +52857,7 @@
         </is>
       </c>
       <c r="G660" s="5" t="n">
-        <v>417</v>
+        <v>2009</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
@@ -53012,19 +52908,15 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>Operating Profit Margin Calculations</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 119 $</t>
-        </is>
-      </c>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Years ended December</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
           <t>-</t>
@@ -53036,7 +52928,7 @@
         </is>
       </c>
       <c r="G661" s="5" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
@@ -53087,12 +52979,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>Operating Profit Margin Calculations</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Divided by revenue 1,407</t>
+          <t>(In millions of dollars) 2009</t>
         </is>
       </c>
       <c r="D662" t="inlineStr"/>
@@ -53107,7 +52999,7 @@
         </is>
       </c>
       <c r="G662" s="5" t="n">
-        <v>1496</v>
+        <v>2008</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
@@ -53158,15 +53050,19 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Years ended December</t>
-        </is>
-      </c>
-      <c r="D663" t="inlineStr"/>
+          <t>Adjusted operating profit $ 4,388 $</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E663" t="inlineStr">
         <is>
           <t>-</t>
@@ -53178,7 +53074,7 @@
         </is>
       </c>
       <c r="G663" s="5" t="n">
-        <v>31</v>
+        <v>4060</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
@@ -53229,15 +53125,19 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>(In millions of dollars, number of shares outstanding in millions) 2009</t>
-        </is>
-      </c>
-      <c r="D664" t="inlineStr"/>
+          <t>Divided by total revenue 11,731</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>
@@ -53249,7 +53149,7 @@
         </is>
       </c>
       <c r="G664" s="5" t="n">
-        <v>2008</v>
+        <v>11335</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
@@ -53300,12 +53200,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
+          <t>WIRELESS</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Operating profit $ 4,316 $</t>
+          <t>Adjusted operating profit $ 3,042 $</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -53324,7 +53224,7 @@
         </is>
       </c>
       <c r="G665" s="5" t="n">
-        <v>4078</v>
+        <v>2806</v>
       </c>
       <c r="H665" t="inlineStr">
         <is>
@@ -53375,12 +53275,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>WIRELESS</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Stock-based compensation expense (recovery) (33)</t>
+          <t>Divided by network revenue 6,245</t>
         </is>
       </c>
       <c r="D666" t="inlineStr"/>
@@ -53395,7 +53295,7 @@
         </is>
       </c>
       <c r="G666" s="5" t="n">
-        <v>-100</v>
+        <v>5843</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -53446,15 +53346,19 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Cable Operations</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Settlement of pension obligations 30</t>
-        </is>
-      </c>
-      <c r="D667" t="inlineStr"/>
+          <t>Adjusted operating profit $ 1,298 $</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E667" t="inlineStr">
         <is>
           <t>-</t>
@@ -53465,10 +53369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G667" s="5" t="n">
+        <v>1171</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
@@ -53519,12 +53421,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Cable Operations</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Integration and restructuring expenses 117</t>
+          <t>Divided by revenue 3,074</t>
         </is>
       </c>
       <c r="D668" t="inlineStr"/>
@@ -53539,7 +53441,7 @@
         </is>
       </c>
       <c r="G668" s="5" t="n">
-        <v>51</v>
+        <v>2878</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
@@ -53590,15 +53492,19 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Rogers Business Solutions</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contract termination fees 19</t>
-        </is>
-      </c>
-      <c r="D669" t="inlineStr"/>
+          <t>Adjusted operating profit $ 35 $</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -53609,10 +53515,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G669" s="5" t="n">
+        <v>59</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
@@ -53663,12 +53567,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Rogers Business Solutions</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Adjustment for CRTC Part II fees decision (61)</t>
+          <t>Divided by revenue 503</t>
         </is>
       </c>
       <c r="D670" t="inlineStr"/>
@@ -53683,7 +53587,7 @@
         </is>
       </c>
       <c r="G670" s="5" t="n">
-        <v>31</v>
+        <v>526</v>
       </c>
       <c r="H670" t="inlineStr">
         <is>
@@ -53734,19 +53638,15 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Rogers Retail</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 4,388 $</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Adjusted operating profit (loss) $ (9) $</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr">
         <is>
           <t>-</t>
@@ -53758,7 +53658,7 @@
         </is>
       </c>
       <c r="G671" s="5" t="n">
-        <v>4060</v>
+        <v>3</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
@@ -53809,19 +53709,15 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>Rogers Retail</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Net income $ 1,478 $</t>
-        </is>
-      </c>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Divided by revenue 399</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
           <t>-</t>
@@ -53833,7 +53729,7 @@
         </is>
       </c>
       <c r="G672" s="5" t="n">
-        <v>1002</v>
+        <v>417</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
@@ -53884,15 +53780,19 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Add (deduct)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Loss on repayment of long-term debt 7</t>
-        </is>
-      </c>
-      <c r="D673" t="inlineStr"/>
+          <t>Adjusted operating profit $ 119 $</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
           <t>-</t>
@@ -53903,10 +53803,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G673" s="5" t="n">
+        <v>142</v>
       </c>
       <c r="H673" t="inlineStr">
         <is>
@@ -53957,12 +53855,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets and other long-term assets 18</t>
+          <t>Divided by revenue 1,407</t>
         </is>
       </c>
       <c r="D674" t="inlineStr"/>
@@ -53977,7 +53875,7 @@
         </is>
       </c>
       <c r="G674" s="5" t="n">
-        <v>294</v>
+        <v>1496</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
@@ -54028,12 +53926,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Debt issuance costs 11</t>
+          <t>Years ended December</t>
         </is>
       </c>
       <c r="D675" t="inlineStr"/>
@@ -54048,7 +53946,7 @@
         </is>
       </c>
       <c r="G675" s="5" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -54099,12 +53997,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Income tax impact (30)</t>
+          <t>(In millions of dollars, number of shares outstanding in millions) 2009</t>
         </is>
       </c>
       <c r="D676" t="inlineStr"/>
@@ -54119,7 +54017,7 @@
         </is>
       </c>
       <c r="G676" s="5" t="n">
-        <v>-34</v>
+        <v>2008</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
@@ -54170,15 +54068,19 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Media adjusted operating profit margin                                                                  8.5%       9.5%</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Adjusted net income $ 1,556 $</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr"/>
+          <t>Operating profit $ 4,316 $</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
           <t>-</t>
@@ -54190,7 +54092,7 @@
         </is>
       </c>
       <c r="G677" s="5" t="n">
-        <v>1260</v>
+        <v>4078</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
@@ -54241,12 +54143,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Adjusted basic and diluted earnings per share</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Adjusted net income $ 1,556 $</t>
+          <t>Stock-based compensation expense (recovery) (33)</t>
         </is>
       </c>
       <c r="D678" t="inlineStr"/>
@@ -54261,7 +54163,7 @@
         </is>
       </c>
       <c r="G678" s="5" t="n">
-        <v>1260</v>
+        <v>-100</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
@@ -54312,19 +54214,15 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number of shares outstanding 621</t>
-        </is>
-      </c>
-      <c r="D679" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Settlement of pension obligations 30</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr">
         <is>
           <t>-</t>
@@ -54335,8 +54233,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G679" s="5" t="n">
-        <v>0.000638</v>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
@@ -54387,12 +54287,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Adjusted basic and diluted earnings per share $ 2.51 $</t>
+          <t>Integration and restructuring expenses 117</t>
         </is>
       </c>
       <c r="D680" t="inlineStr"/>
@@ -54407,7 +54307,7 @@
         </is>
       </c>
       <c r="G680" s="5" t="n">
-        <v>1.98e-06</v>
+        <v>51</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
@@ -54458,12 +54358,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Wireless Non-Gaap Calculations</t>
+          <t>Contract termination fees 19</t>
         </is>
       </c>
       <c r="D681" t="inlineStr"/>
@@ -54477,8 +54377,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G681" s="5" t="n">
-        <v>-1</v>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
@@ -54529,12 +54431,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Years ended December</t>
+          <t>Adjustment for CRTC Part II fees decision (61)</t>
         </is>
       </c>
       <c r="D682" t="inlineStr"/>
@@ -54600,15 +54502,19 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Divided by: weighted average number</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>(In millions of dollars, subscribers in thousands, except ARPU figures and adjusted operating profit margin) 2009</t>
-        </is>
-      </c>
-      <c r="D683" t="inlineStr"/>
+          <t>Adjusted operating profit $ 4,388 $</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
           <t>-</t>
@@ -54620,7 +54526,7 @@
         </is>
       </c>
       <c r="G683" s="5" t="n">
-        <v>2008</v>
+        <v>4060</v>
       </c>
       <c r="H683" t="inlineStr">
         <is>
@@ -54671,15 +54577,19 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Postpaid ARPU (monthly)</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Postpaid (voice and data) revenue $ 5,948 $</t>
-        </is>
-      </c>
-      <c r="D684" t="inlineStr"/>
+          <t>Net income $ 1,478 $</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E684" t="inlineStr">
         <is>
           <t>-</t>
@@ -54691,7 +54601,7 @@
         </is>
       </c>
       <c r="G684" s="5" t="n">
-        <v>5558</v>
+        <v>1002</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -54742,12 +54652,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Postpaid ARPU (monthly)</t>
+          <t>Add (deduct)</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Divided by: average postpaid wireless voice and data subscribers 6,705</t>
+          <t>Loss on repayment of long-term debt 7</t>
         </is>
       </c>
       <c r="D685" t="inlineStr"/>
@@ -54761,8 +54671,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G685" s="5" t="n">
-        <v>6142</v>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
@@ -54813,12 +54725,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Postpaid ARPU (monthly)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Divided by: 12 months 12</t>
+          <t>Impairment losses on goodwill, intangible assets and other long-term assets 18</t>
         </is>
       </c>
       <c r="D686" t="inlineStr"/>
@@ -54833,7 +54745,7 @@
         </is>
       </c>
       <c r="G686" s="5" t="n">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
@@ -54884,12 +54796,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Postpaid ARPU (monthly)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Postpaid ARPU (monthly) total</t>
+          <t>Debt issuance costs 11</t>
         </is>
       </c>
       <c r="D687" t="inlineStr"/>
@@ -54904,7 +54816,7 @@
         </is>
       </c>
       <c r="G687" s="5" t="n">
-        <v>75.41</v>
+        <v>16</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
@@ -54955,12 +54867,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Prepaid ARPU (monthly)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Prepaid (voice and data) revenue $ 297 $</t>
+          <t>Income tax impact (30)</t>
         </is>
       </c>
       <c r="D688" t="inlineStr"/>
@@ -54975,7 +54887,7 @@
         </is>
       </c>
       <c r="G688" s="5" t="n">
-        <v>285</v>
+        <v>-34</v>
       </c>
       <c r="H688" t="inlineStr">
         <is>
@@ -55026,12 +54938,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Prepaid ARPU (monthly)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Divided by: average prepaid subscribers 1,479</t>
+          <t>Adjusted net income $ 1,556 $</t>
         </is>
       </c>
       <c r="D689" t="inlineStr"/>
@@ -55046,7 +54958,7 @@
         </is>
       </c>
       <c r="G689" s="5" t="n">
-        <v>1426</v>
+        <v>1260</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
@@ -55097,12 +55009,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Prepaid ARPU (monthly)</t>
+          <t>Adjusted basic and diluted earnings per share</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Divided by: 12 months 12</t>
+          <t>Adjusted net income $ 1,556 $</t>
         </is>
       </c>
       <c r="D690" t="inlineStr"/>
@@ -55117,7 +55029,7 @@
         </is>
       </c>
       <c r="G690" s="5" t="n">
-        <v>12</v>
+        <v>1260</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
@@ -55168,15 +55080,19 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Prepaid ARPU (monthly)</t>
+          <t>Divided by: weighted average number</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Prepaid ARPU (monthly) total</t>
-        </is>
-      </c>
-      <c r="D691" t="inlineStr"/>
+          <t>Divided by: weighted average number of shares outstanding 621</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
           <t>-</t>
@@ -55188,7 +55104,7 @@
         </is>
       </c>
       <c r="G691" s="5" t="n">
-        <v>16.65</v>
+        <v>0.000638</v>
       </c>
       <c r="H691" t="inlineStr">
         <is>
@@ -55239,12 +55155,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Blended ARPU (monthly)</t>
+          <t>Divided by: weighted average number</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Voice and data revenue $ 6,245 $</t>
+          <t>Adjusted basic and diluted earnings per share $ 2.51 $</t>
         </is>
       </c>
       <c r="D692" t="inlineStr"/>
@@ -55259,7 +55175,7 @@
         </is>
       </c>
       <c r="G692" s="5" t="n">
-        <v>5843</v>
+        <v>1.98e-06</v>
       </c>
       <c r="H692" t="inlineStr">
         <is>
@@ -55310,12 +55226,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Blended ARPU (monthly)</t>
+          <t>Divided by: weighted average number</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Divided by: average wireless voice and data subscribers 8,184</t>
+          <t>Wireless Non-Gaap Calculations</t>
         </is>
       </c>
       <c r="D693" t="inlineStr"/>
@@ -55330,7 +55246,7 @@
         </is>
       </c>
       <c r="G693" s="5" t="n">
-        <v>7568</v>
+        <v>-1</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -55381,12 +55297,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Blended ARPU (monthly)</t>
+          <t>Divided by: weighted average number</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Divided by: 12 months 12</t>
+          <t>Years ended December</t>
         </is>
       </c>
       <c r="D694" t="inlineStr"/>
@@ -55401,7 +55317,7 @@
         </is>
       </c>
       <c r="G694" s="5" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
@@ -55452,12 +55368,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Blended ARPU (monthly)</t>
+          <t>Divided by: weighted average number</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Blended ARPU (monthly) total</t>
+          <t>(In millions of dollars, subscribers in thousands, except ARPU figures and adjusted operating profit margin) 2009</t>
         </is>
       </c>
       <c r="D695" t="inlineStr"/>
@@ -55472,7 +55388,7 @@
         </is>
       </c>
       <c r="G695" s="5" t="n">
-        <v>64.34</v>
+        <v>2008</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
@@ -55523,19 +55439,15 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Adjusted operating profit margin</t>
+          <t>Postpaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Adjusted operating profit $ 3,042 $</t>
-        </is>
-      </c>
-      <c r="D696" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Postpaid (voice and data) revenue $ 5,948 $</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr">
         <is>
           <t>-</t>
@@ -55547,7 +55459,7 @@
         </is>
       </c>
       <c r="G696" s="5" t="n">
-        <v>2806</v>
+        <v>5558</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
@@ -55598,12 +55510,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Adjusted operating profit margin</t>
+          <t>Postpaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Divided by: network revenue 6,245</t>
+          <t>Divided by: average postpaid wireless voice and data subscribers 6,705</t>
         </is>
       </c>
       <c r="D697" t="inlineStr"/>
@@ -55618,7 +55530,7 @@
         </is>
       </c>
       <c r="G697" s="5" t="n">
-        <v>5843</v>
+        <v>6142</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
@@ -55669,12 +55581,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Adjusted operating profit margin                                                                    48.7%      48.0%</t>
+          <t>Postpaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Years ended December 31, 2009 and 2008 2009</t>
+          <t>Divided by: 12 months 12</t>
         </is>
       </c>
       <c r="D698" t="inlineStr"/>
@@ -55689,7 +55601,7 @@
         </is>
       </c>
       <c r="G698" s="5" t="n">
-        <v>2008</v>
+        <v>12</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
@@ -55740,19 +55652,15 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Adjusted operating profit margin                                                                    48.7%      48.0%</t>
+          <t>Postpaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Operating revenue (note 3(b)) $ 11,731 $</t>
-        </is>
-      </c>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>OperatingRevenue</t>
-        </is>
-      </c>
+          <t>Postpaid ARPU (monthly) total</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr">
         <is>
           <t>-</t>
@@ -55764,7 +55672,7 @@
         </is>
       </c>
       <c r="G699" s="5" t="n">
-        <v>11335</v>
+        <v>75.41</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
@@ -55815,19 +55723,15 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Prepaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Cost of sales 1,380</t>
-        </is>
-      </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Prepaid (voice and data) revenue $ 297 $</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
           <t>-</t>
@@ -55839,7 +55743,7 @@
         </is>
       </c>
       <c r="G700" s="5" t="n">
-        <v>1303</v>
+        <v>285</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
@@ -55890,19 +55794,15 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Prepaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Sales and marketing 1,207</t>
-        </is>
-      </c>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
+          <t>Divided by: average prepaid subscribers 1,479</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr">
         <is>
           <t>-</t>
@@ -55914,7 +55814,7 @@
         </is>
       </c>
       <c r="G701" s="5" t="n">
-        <v>1334</v>
+        <v>1426</v>
       </c>
       <c r="H701" t="inlineStr">
         <is>
@@ -55965,19 +55865,15 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Prepaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Operating, general and administrative 4,681</t>
-        </is>
-      </c>
-      <c r="D702" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Divided by: 12 months 12</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
           <t>-</t>
@@ -55989,7 +55885,7 @@
         </is>
       </c>
       <c r="G702" s="5" t="n">
-        <v>4569</v>
+        <v>12</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -56040,12 +55936,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Prepaid ARPU (monthly)</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Settlement of pension obligations (note 17(d)) 30</t>
+          <t>Prepaid ARPU (monthly) total</t>
         </is>
       </c>
       <c r="D703" t="inlineStr"/>
@@ -56059,10 +55955,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G703" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G703" s="5" t="n">
+        <v>16.65</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
@@ -56113,12 +56007,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Blended ARPU (monthly)</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Integration and restructuring (note 6) 117</t>
+          <t>Voice and data revenue $ 6,245 $</t>
         </is>
       </c>
       <c r="D704" t="inlineStr"/>
@@ -56133,7 +56027,7 @@
         </is>
       </c>
       <c r="G704" s="5" t="n">
-        <v>51</v>
+        <v>5843</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
@@ -56184,19 +56078,15 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Blended ARPU (monthly)</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 1,730</t>
-        </is>
-      </c>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Divided by: average wireless voice and data subscribers 8,184</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>-</t>
@@ -56208,7 +56098,7 @@
         </is>
       </c>
       <c r="G705" s="5" t="n">
-        <v>1760</v>
+        <v>7568</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
@@ -56259,12 +56149,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Blended ARPU (monthly)</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets and other long-term assets (notes 11(a) and 13) 18</t>
+          <t>Divided by: 12 months 12</t>
         </is>
       </c>
       <c r="D706" t="inlineStr"/>
@@ -56279,7 +56169,7 @@
         </is>
       </c>
       <c r="G706" s="5" t="n">
-        <v>294</v>
+        <v>12</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
@@ -56330,19 +56220,15 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Blended ARPU (monthly)</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Operating income 2,568</t>
-        </is>
-      </c>
-      <c r="D707" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Blended ARPU (monthly) total</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr">
         <is>
           <t>-</t>
@@ -56354,7 +56240,7 @@
         </is>
       </c>
       <c r="G707" s="5" t="n">
-        <v>2024</v>
+        <v>64.34</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
@@ -56405,15 +56291,19 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Adjusted operating profit margin</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Interest on long-term debt (647)</t>
-        </is>
-      </c>
-      <c r="D708" t="inlineStr"/>
+          <t>Adjusted operating profit $ 3,042 $</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E708" t="inlineStr">
         <is>
           <t>-</t>
@@ -56425,7 +56315,7 @@
         </is>
       </c>
       <c r="G708" s="5" t="n">
-        <v>-575</v>
+        <v>2806</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
@@ -56476,12 +56366,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Adjusted operating profit margin</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Debt issuance costs (note 14(a)) (11)</t>
+          <t>Divided by: network revenue 6,245</t>
         </is>
       </c>
       <c r="D709" t="inlineStr"/>
@@ -56496,7 +56386,7 @@
         </is>
       </c>
       <c r="G709" s="5" t="n">
-        <v>-16</v>
+        <v>5843</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
@@ -56547,19 +56437,15 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Adjusted operating profit margin                                                                    48.7%      48.0%</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss) 136</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Years ended December 31, 2009 and 2008 2009</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr">
         <is>
           <t>-</t>
@@ -56571,7 +56457,7 @@
         </is>
       </c>
       <c r="G710" s="5" t="n">
-        <v>-99</v>
+        <v>2008</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
@@ -56622,15 +56508,19 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Adjusted operating profit margin                                                                    48.7%      48.0%</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Loss on repayment of long-term debt (note 14(c)) (7)</t>
-        </is>
-      </c>
-      <c r="D711" t="inlineStr"/>
+          <t>Operating revenue (note 3(b)) $ 11,731 $</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>OperatingRevenue</t>
+        </is>
+      </c>
       <c r="E711" t="inlineStr">
         <is>
           <t>-</t>
@@ -56641,10 +56531,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G711" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G711" s="5" t="n">
+        <v>11335</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -56695,15 +56583,19 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Change in fair value of derivative instruments (65)</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr"/>
+          <t>Cost of sales 1,380</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
@@ -56715,7 +56607,7 @@
         </is>
       </c>
       <c r="G712" s="5" t="n">
-        <v>64</v>
+        <v>1303</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
@@ -56766,17 +56658,17 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Other income 6</t>
+          <t>Sales and marketing 1,207</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingAndMarketingExpense</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -56790,7 +56682,7 @@
         </is>
       </c>
       <c r="G713" s="5" t="n">
-        <v>28</v>
+        <v>1334</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
@@ -56841,17 +56733,17 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Impairment losses on goodwill, intangible assets</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Income before income taxes 1,980</t>
+          <t>Operating, general and administrative 4,681</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -56865,7 +56757,7 @@
         </is>
       </c>
       <c r="G714" s="5" t="n">
-        <v>1426</v>
+        <v>4569</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
@@ -56916,12 +56808,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Current 215</t>
+          <t>Settlement of pension obligations (note 17(d)) 30</t>
         </is>
       </c>
       <c r="D715" t="inlineStr"/>
@@ -56935,8 +56827,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G715" s="5" t="n">
-        <v>3</v>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
@@ -56987,12 +56881,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Future 287</t>
+          <t>Integration and restructuring (note 6) 117</t>
         </is>
       </c>
       <c r="D716" t="inlineStr"/>
@@ -57007,7 +56901,7 @@
         </is>
       </c>
       <c r="G716" s="5" t="n">
-        <v>421</v>
+        <v>51</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
@@ -57058,15 +56952,19 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Income tax expense total</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr"/>
+          <t>Depreciation and amortization 1,730</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E717" t="inlineStr">
         <is>
           <t>-</t>
@@ -57078,7 +56976,7 @@
         </is>
       </c>
       <c r="G717" s="5" t="n">
-        <v>424</v>
+        <v>1760</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
@@ -57129,19 +57027,15 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Net income for the year $ 1,478 $</t>
-        </is>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment losses on goodwill, intangible assets and other long-term assets (notes 11(a) and 13) 18</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
           <t>-</t>
@@ -57153,7 +57047,7 @@
         </is>
       </c>
       <c r="G718" s="5" t="n">
-        <v>1002</v>
+        <v>294</v>
       </c>
       <c r="H718" t="inlineStr">
         <is>
@@ -57204,15 +57098,19 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Basic and diluted $ 2.38 $</t>
-        </is>
-      </c>
-      <c r="D719" t="inlineStr"/>
+          <t>Operating income 2,568</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>-</t>
@@ -57224,7 +57122,7 @@
         </is>
       </c>
       <c r="G719" s="5" t="n">
-        <v>1.57</v>
+        <v>2024</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
@@ -57275,12 +57173,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Years ended December 31, 2009 and 2008 2009</t>
+          <t>Interest on long-term debt (647)</t>
         </is>
       </c>
       <c r="D720" t="inlineStr"/>
@@ -57295,7 +57193,7 @@
         </is>
       </c>
       <c r="G720" s="5" t="n">
-        <v>2008</v>
+        <v>-575</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -57346,19 +57244,15 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Net income for the year $ 1,478 $</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Debt issuance costs (note 14(a)) (11)</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
           <t>-</t>
@@ -57370,7 +57264,7 @@
         </is>
       </c>
       <c r="G721" s="5" t="n">
-        <v>1002</v>
+        <v>-16</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
@@ -57421,15 +57315,19 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Increase (decrease) in fair value of available-for-sale investments 14</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr"/>
+          <t>Foreign exchange gain (loss) 136</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E722" t="inlineStr">
         <is>
           <t>-</t>
@@ -57441,7 +57339,7 @@
         </is>
       </c>
       <c r="G722" s="5" t="n">
-        <v>-146</v>
+        <v>-99</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
@@ -57492,12 +57390,12 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Change in fair value of derivative instruments (844)</t>
+          <t>Loss on repayment of long-term debt (note 14(c)) (7)</t>
         </is>
       </c>
       <c r="D723" t="inlineStr"/>
@@ -57511,8 +57409,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G723" s="5" t="n">
-        <v>1122</v>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
@@ -57563,12 +57463,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Reclassification to net income of foreign exchange gain (loss) on long-term debt 901</t>
+          <t>Change in fair value of derivative instruments (65)</t>
         </is>
       </c>
       <c r="D724" t="inlineStr"/>
@@ -57583,7 +57483,7 @@
         </is>
       </c>
       <c r="G724" s="5" t="n">
-        <v>-1274</v>
+        <v>64</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
@@ -57634,15 +57534,19 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Reclassification to net income of accrued interest 64</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr"/>
+          <t>Other income 6</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -57654,7 +57558,7 @@
         </is>
       </c>
       <c r="G725" s="5" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
@@ -57705,15 +57609,19 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Impairment losses on goodwill, intangible assets</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments total</t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr"/>
+          <t>Income before income taxes 1,980</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
           <t>-</t>
@@ -57725,7 +57633,7 @@
         </is>
       </c>
       <c r="G726" s="5" t="n">
-        <v>-42</v>
+        <v>1426</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
@@ -57776,19 +57684,15 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss) before income taxes 135</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Current 215</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
           <t>-</t>
@@ -57800,7 +57704,7 @@
         </is>
       </c>
       <c r="G727" s="5" t="n">
-        <v>-188</v>
+        <v>3</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
@@ -57851,12 +57755,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Related income tax recovery 3</t>
+          <t>Future 287</t>
         </is>
       </c>
       <c r="D728" t="inlineStr"/>
@@ -57871,7 +57775,7 @@
         </is>
       </c>
       <c r="G728" s="5" t="n">
-        <v>43</v>
+        <v>421</v>
       </c>
       <c r="H728" t="inlineStr">
         <is>
@@ -57922,12 +57826,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Cash flow hedging derivative instruments</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Comprehensive income for the year $ 1,616 $</t>
+          <t>Income tax expense total</t>
         </is>
       </c>
       <c r="D729" t="inlineStr"/>
@@ -57942,44 +57846,912 @@
         </is>
       </c>
       <c r="G729" s="5" t="n">
+        <v>424</v>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Net income for the year $ 1,478 $</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G730" s="5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Basic and diluted $ 2.38 $</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G731" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Years ended December 31, 2009 and 2008 2009</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G732" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Net income for the year $ 1,478 $</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G733" s="5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in fair value of available-for-sale investments 14</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G734" s="5" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Change in fair value of derivative instruments (844)</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G735" s="5" t="n">
+        <v>1122</v>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Reclassification to net income of foreign exchange gain (loss) on long-term debt 901</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G736" s="5" t="n">
+        <v>-1274</v>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Reclassification to net income of accrued interest 64</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G737" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments total</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G738" s="5" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss) before income taxes 135</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G739" s="5" t="n">
+        <v>-188</v>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Related income tax recovery 3</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G740" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Cash flow hedging derivative instruments</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Comprehensive income for the year $ 1,616 $</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G741" s="5" t="n">
         <v>857</v>
       </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O729" t="inlineStr">
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
         <is>
           <t>-</t>
         </is>
